--- a/public/excel/website-data.xlsx
+++ b/public/excel/website-data.xlsx
@@ -592,7 +592,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -628,119 +628,127 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>active_batch_title</v>
+        <v>hero_video_url</v>
       </c>
       <c r="B5" t="str">
-        <v>Active Batch</v>
+        <v>https://www.youtube.com/watch?v=szj5j8-9L_c</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>active_batch_branch</v>
+        <v>active_batch_title</v>
       </c>
       <c r="B6" t="str">
-        <v>Electrical Engineering</v>
+        <v>Active Batch</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>active_batch_semester</v>
+        <v>active_batch_branch</v>
       </c>
       <c r="B7" t="str">
-        <v>4th Semester</v>
+        <v>Electrical Engineering</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>active_batch_session</v>
+        <v>active_batch_semester</v>
       </c>
       <c r="B8" t="str">
-        <v>Session 2024-2027</v>
+        <v>4th Semester</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>active_batch_button</v>
+        <v>active_batch_session</v>
       </c>
       <c r="B9" t="str">
-        <v>Join Now</v>
+        <v>Session 2024-2027</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>active_batch_form</v>
+        <v>active_batch_button</v>
       </c>
       <c r="B10" t="str">
-        <v>https://forms.google.com</v>
+        <v>Join Now</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>coming_batch_title</v>
+        <v>active_batch_form</v>
       </c>
       <c r="B11" t="str">
-        <v>Coming Soon</v>
+        <v>https://forms.google.com</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>coming_batch_branch</v>
+        <v>coming_batch_title</v>
       </c>
       <c r="B12" t="str">
-        <v>1st Semester</v>
+        <v>Coming Soon</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>coming_batch_semester</v>
+        <v>coming_batch_branch</v>
       </c>
       <c r="B13" t="str">
-        <v>All Branches</v>
+        <v>1st Semester</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>coming_batch_session</v>
+        <v>coming_batch_semester</v>
       </c>
       <c r="B14" t="str">
-        <v>Session 2026-2029</v>
+        <v>All Branches</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>coming_batch_button</v>
+        <v>coming_batch_session</v>
       </c>
       <c r="B15" t="str">
-        <v>Register Now</v>
+        <v>Session 2026-2029</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>coming_batch_form</v>
+        <v>coming_batch_button</v>
       </c>
       <c r="B16" t="str">
-        <v>https://forms.google.com</v>
+        <v>Register Now</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>why_choose_us</v>
+        <v>coming_batch_form</v>
       </c>
       <c r="B17" t="str">
-        <v>Live Classes|Easy Teaching|Complete Syllabus|Handwritten Notes|PDF Notes|Practice Questions|Doubt Solving|Affordable Fees|Mobile Friendly|Personal Support</v>
+        <v>https://forms.google.com</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
+        <v>why_choose_us</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Live Classes|Easy Teaching|Complete Syllabus|Handwritten Notes|PDF Notes|Practice Questions|Doubt Solving|Affordable Fees|Mobile Friendly|Personal Support</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
         <v>enrollment_steps</v>
       </c>
-      <c r="B18" t="str">
+      <c r="B19" t="str">
         <v>Click Join Now|Google Form Opens|Fill Student Details|Pay Fees|Upload Payment Screenshot|Submit|Receive WhatsApp Confirmation</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B19"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/public/excel/website-data.xlsx
+++ b/public/excel/website-data.xlsx
@@ -991,35 +991,171 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:J5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>key</v>
+        <v>Status</v>
       </c>
       <c r="B1" t="str">
-        <v>value</v>
+        <v>Title</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Branch</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Semester</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Session</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Fees</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Timing</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Form URL</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Button</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>active_batch_form</v>
+        <v>active</v>
       </c>
       <c r="B2" t="str">
+        <v>Active Batch</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Electrical Engineering</v>
+      </c>
+      <c r="D2" t="str">
+        <v>4th Semester</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Session 2024-2027</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Full syllabus live classes with notes, practice questions, and doubt support.</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Contact for fees</v>
+      </c>
+      <c r="H2" t="str">
+        <v>7:00 PM</v>
+      </c>
+      <c r="I2" t="str">
         <v>https://forms.google.com</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Join Now</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>coming_batch_form</v>
+        <v>active</v>
       </c>
       <c r="B3" t="str">
+        <v>Active Batch</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Electrical &amp; Electronics Engineering</v>
+      </c>
+      <c r="D3" t="str">
+        <v>4th Semester</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Session 2024-2027</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Subject-wise support with weekly practice and doubt clearing.</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Contact for fees</v>
+      </c>
+      <c r="H3" t="str">
+        <v>8:00 PM</v>
+      </c>
+      <c r="I3" t="str">
         <v>https://forms.google.com</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Join Now</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>upcoming</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Coming Soon</v>
+      </c>
+      <c r="C4" t="str">
+        <v>1st Semester</v>
+      </c>
+      <c r="D4" t="str">
+        <v>All Branches</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Session 2026-2029</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Foundation batch for new diploma students.</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Announcing soon</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Coming soon</v>
+      </c>
+      <c r="I4" t="str">
+        <v>https://forms.google.com</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Register Now</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>upcoming</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Coming Soon</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Civil Engineering</v>
+      </c>
+      <c r="D5" t="str">
+        <v>3rd Semester</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Session 2025-2028</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Upcoming civil branch semester batch.</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Announcing soon</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Coming soon</v>
+      </c>
+      <c r="I5" t="str">
+        <v>https://forms.google.com</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Register Now</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
   </ignoredErrors>
 </worksheet>
 </file>
